--- a/ROSA_vitaSPEC/Results/test_pretraitements/C14.0/CAROT_/CAROT_Resultats_C14.0_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/C14.0/CAROT_/CAROT_Resultats_C14.0_moy_RMSEP.xlsx
@@ -1,21 +1,223 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\C14.0\CAROT_\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>RMSEP_glo</t>
+  </si>
+  <si>
+    <t>LV0_RMSEP</t>
+  </si>
+  <si>
+    <t>LV1_RMSEP</t>
+  </si>
+  <si>
+    <t>LV2_RMSEP</t>
+  </si>
+  <si>
+    <t>LV3_RMSEP</t>
+  </si>
+  <si>
+    <t>LV4_RMSEP</t>
+  </si>
+  <si>
+    <t>LV5_RMSEP</t>
+  </si>
+  <si>
+    <t>LV6_RMSEP</t>
+  </si>
+  <si>
+    <t>LV7_RMSEP</t>
+  </si>
+  <si>
+    <t>LV8_RMSEP</t>
+  </si>
+  <si>
+    <t>LV9_RMSEP</t>
+  </si>
+  <si>
+    <t>LV10_RMSEP</t>
+  </si>
+  <si>
+    <t>LV11_RMSEP</t>
+  </si>
+  <si>
+    <t>LV12_RMSEP</t>
+  </si>
+  <si>
+    <t>LV13_RMSEP</t>
+  </si>
+  <si>
+    <t>LV14_RMSEP</t>
+  </si>
+  <si>
+    <t>LV15_RMSEP</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,11 +265,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +319,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +351,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +386,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,369 +562,328 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>RMSEP_glo</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV0_RMSEP</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_RMSEP</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_RMSEP</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_RMSEP</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_RMSEP</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_RMSEP</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_RMSEP</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_RMSEP</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_RMSEP</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_RMSEP</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_RMSEP</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_RMSEP</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_RMSEP</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_RMSEP</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_RMSEP</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_RMSEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
       </c>
       <c r="B2">
-        <v>0.2997868105929278</v>
+        <v>0.29978681059292778</v>
       </c>
       <c r="C2">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D2">
-        <v>0.3562292436257328</v>
+        <v>0.35622924362573283</v>
       </c>
       <c r="E2">
-        <v>0.3547911027041935</v>
+        <v>0.35479110270419351</v>
       </c>
       <c r="F2">
-        <v>0.3524660694400442</v>
+        <v>0.35246606944004422</v>
       </c>
       <c r="G2">
-        <v>0.343968216959728</v>
+        <v>0.34396821695972801</v>
       </c>
       <c r="H2">
-        <v>0.336338499228946</v>
+        <v>0.33633849922894599</v>
       </c>
       <c r="I2">
-        <v>0.3209759861617159</v>
+        <v>0.32097598616171591</v>
       </c>
       <c r="J2">
-        <v>0.3039558615983544</v>
+        <v>0.30395586159835442</v>
       </c>
       <c r="K2">
-        <v>0.2929004071635158</v>
+        <v>0.29290040716351579</v>
       </c>
       <c r="L2">
-        <v>0.2887544107659585</v>
+        <v>0.28875441076595848</v>
       </c>
       <c r="M2">
         <v>0.2823088877948397</v>
       </c>
       <c r="N2">
-        <v>0.280648191846176</v>
+        <v>0.28064819184617601</v>
       </c>
       <c r="O2">
-        <v>0.2793921606682878</v>
+        <v>0.27939216066828781</v>
       </c>
       <c r="P2">
-        <v>0.2796909592381605</v>
+        <v>0.27969095923816051</v>
       </c>
       <c r="Q2">
         <v>0.2827984249263133</v>
       </c>
       <c r="R2">
-        <v>0.2906559932119117</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.29065599321191171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
       </c>
       <c r="B3">
-        <v>0.3129665977819014</v>
+        <v>0.31296659778190139</v>
       </c>
       <c r="C3">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D3">
-        <v>0.3577511227751066</v>
+        <v>0.35775112277510662</v>
       </c>
       <c r="E3">
-        <v>0.3570930345965239</v>
+        <v>0.35709303459652392</v>
       </c>
       <c r="F3">
-        <v>0.3553010813548704</v>
+        <v>0.35530108135487037</v>
       </c>
       <c r="G3">
-        <v>0.3439527814747032</v>
+        <v>0.34395278147470321</v>
       </c>
       <c r="H3">
-        <v>0.3202206587285003</v>
+        <v>0.32022065872850031</v>
       </c>
       <c r="I3">
-        <v>0.3089132047536258</v>
+        <v>0.30891320475362583</v>
       </c>
       <c r="J3">
-        <v>0.3047547715678049</v>
+        <v>0.30475477156780489</v>
       </c>
       <c r="K3">
-        <v>0.2977094997240242</v>
+        <v>0.29770949972402422</v>
       </c>
       <c r="L3">
-        <v>0.2941734052801322</v>
+        <v>0.29417340528013219</v>
       </c>
       <c r="M3">
         <v>0.2878975157833204</v>
       </c>
       <c r="N3">
-        <v>0.2889973244157489</v>
+        <v>0.28899732441574888</v>
       </c>
       <c r="O3">
-        <v>0.28701713855036</v>
+        <v>0.28701713855035998</v>
       </c>
       <c r="P3">
         <v>0.2918955377763584</v>
       </c>
       <c r="Q3">
-        <v>0.3007409791276106</v>
+        <v>0.30074097912761061</v>
       </c>
       <c r="R3">
-        <v>0.3084801638094709</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.30848016380947091</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
       </c>
       <c r="B4">
-        <v>0.3412021819251753</v>
+        <v>0.34120218192517532</v>
       </c>
       <c r="C4">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D4">
-        <v>0.3582257135188086</v>
+        <v>0.35822571351880861</v>
       </c>
       <c r="E4">
-        <v>0.3623395523197744</v>
+        <v>0.36233955231977438</v>
       </c>
       <c r="F4">
-        <v>0.3568600405611531</v>
+        <v>0.35686004056115311</v>
       </c>
       <c r="G4">
-        <v>0.3572141623882529</v>
+        <v>0.35721416238825288</v>
       </c>
       <c r="H4">
-        <v>0.3507481058929419</v>
+        <v>0.35074810589294192</v>
       </c>
       <c r="I4">
-        <v>0.3316916939768345</v>
+        <v>0.33169169397683451</v>
       </c>
       <c r="J4">
-        <v>0.3262096139069974</v>
+        <v>0.32620961390699738</v>
       </c>
       <c r="K4">
-        <v>0.3154683729884211</v>
+        <v>0.31546837298842112</v>
       </c>
       <c r="L4">
-        <v>0.3179993830465132</v>
+        <v>0.31799938304651321</v>
       </c>
       <c r="M4">
-        <v>0.3212433151188029</v>
+        <v>0.32124331511880289</v>
       </c>
       <c r="N4">
-        <v>0.3248159448823942</v>
+        <v>0.32481594488239418</v>
       </c>
       <c r="O4">
-        <v>0.3275061778919254</v>
+        <v>0.32750617789192538</v>
       </c>
       <c r="P4">
-        <v>0.3233152343050396</v>
+        <v>0.32331523430503961</v>
       </c>
       <c r="Q4">
-        <v>0.3199342505831667</v>
+        <v>0.31993425058316671</v>
       </c>
       <c r="R4">
-        <v>0.3250563393219615</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.32505633932196148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
       </c>
       <c r="B5">
-        <v>0.3318554350767421</v>
+        <v>0.33185543507674209</v>
       </c>
       <c r="C5">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D5">
-        <v>0.3580058341732831</v>
+        <v>0.35800583417328308</v>
       </c>
       <c r="E5">
-        <v>0.3582404942859975</v>
+        <v>0.35824049428599752</v>
       </c>
       <c r="F5">
-        <v>0.3580408078811532</v>
+        <v>0.35804080788115322</v>
       </c>
       <c r="G5">
-        <v>0.3496098557994838</v>
+        <v>0.34960985579948378</v>
       </c>
       <c r="H5">
-        <v>0.3439471299544875</v>
+        <v>0.34394712995448751</v>
       </c>
       <c r="I5">
-        <v>0.3208076379918228</v>
+        <v>0.32080763799182282</v>
       </c>
       <c r="J5">
-        <v>0.3231064282590067</v>
+        <v>0.32310642825900671</v>
       </c>
       <c r="K5">
-        <v>0.3239512228967829</v>
+        <v>0.32395122289678291</v>
       </c>
       <c r="L5">
-        <v>0.3155580407440691</v>
+        <v>0.31555804074406912</v>
       </c>
       <c r="M5">
         <v>0.3097956023724483</v>
       </c>
       <c r="N5">
-        <v>0.3082516502813026</v>
+        <v>0.30825165028130258</v>
       </c>
       <c r="O5">
-        <v>0.3046999062140097</v>
+        <v>0.30469990621400972</v>
       </c>
       <c r="P5">
-        <v>0.3023944160623001</v>
+        <v>0.30239441606230011</v>
       </c>
       <c r="Q5">
-        <v>0.3040920986055544</v>
+        <v>0.30409209860555442</v>
       </c>
       <c r="R5">
-        <v>0.3079915830586112</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.30799158305861118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
       </c>
       <c r="B6">
-        <v>0.3075264192271407</v>
+        <v>0.30752641922714069</v>
       </c>
       <c r="C6">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D6">
-        <v>0.3575981999969038</v>
+        <v>0.35759819999690379</v>
       </c>
       <c r="E6">
-        <v>0.3566096689005664</v>
+        <v>0.35660966890056639</v>
       </c>
       <c r="F6">
         <v>0.3538805069637605</v>
       </c>
       <c r="G6">
-        <v>0.3320139367640779</v>
+        <v>0.33201393676407792</v>
       </c>
       <c r="H6">
-        <v>0.3339986009571009</v>
+        <v>0.33399860095710088</v>
       </c>
       <c r="I6">
-        <v>0.3126687637119251</v>
+        <v>0.31266876371192509</v>
       </c>
       <c r="J6">
-        <v>0.3160317288888794</v>
+        <v>0.31603172888887943</v>
       </c>
       <c r="K6">
-        <v>0.3080202729216983</v>
+        <v>0.30802027292169831</v>
       </c>
       <c r="L6">
         <v>0.2926074691017973</v>
@@ -721,795 +892,767 @@
         <v>0.2912733612813741</v>
       </c>
       <c r="N6">
-        <v>0.2890502103878907</v>
+        <v>0.28905021038789069</v>
       </c>
       <c r="O6">
-        <v>0.2823884526817189</v>
+        <v>0.28238845268171892</v>
       </c>
       <c r="P6">
-        <v>0.2856110451692715</v>
+        <v>0.28561104516927149</v>
       </c>
       <c r="Q6">
-        <v>0.2915349765442947</v>
+        <v>0.29153497654429472</v>
       </c>
       <c r="R6">
-        <v>0.2960491187890757</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.29604911878907569</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
       </c>
       <c r="B7">
-        <v>0.326083369225016</v>
+        <v>0.32608336922501602</v>
       </c>
       <c r="C7">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D7">
-        <v>0.3587161090576761</v>
+        <v>0.35871610905767609</v>
       </c>
       <c r="E7">
-        <v>0.36366636350524</v>
+        <v>0.36366636350524001</v>
       </c>
       <c r="F7">
-        <v>0.3562376426817582</v>
+        <v>0.35623764268175823</v>
       </c>
       <c r="G7">
-        <v>0.3588385428319628</v>
+        <v>0.35883854283196281</v>
       </c>
       <c r="H7">
-        <v>0.3552049362110367</v>
+        <v>0.35520493621103671</v>
       </c>
       <c r="I7">
-        <v>0.3410663535682557</v>
+        <v>0.34106635356825571</v>
       </c>
       <c r="J7">
         <v>0.3164868331389788</v>
       </c>
       <c r="K7">
-        <v>0.3175229148575661</v>
+        <v>0.31752291485756612</v>
       </c>
       <c r="L7">
-        <v>0.3086025746679852</v>
+        <v>0.30860257466798519</v>
       </c>
       <c r="M7">
-        <v>0.3102827099064495</v>
+        <v>0.31028270990644952</v>
       </c>
       <c r="N7">
-        <v>0.3112489384129793</v>
+        <v>0.31124893841297929</v>
       </c>
       <c r="O7">
-        <v>0.3189728491487664</v>
+        <v>0.31897284914876639</v>
       </c>
       <c r="P7">
-        <v>0.3211956151569035</v>
+        <v>0.32119561515690348</v>
       </c>
       <c r="Q7">
-        <v>0.3150913129375303</v>
+        <v>0.31509131293753029</v>
       </c>
       <c r="R7">
-        <v>0.3121022541545295</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.31210225415452952</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
       </c>
       <c r="B8">
-        <v>0.328325329931359</v>
+        <v>0.32832532993135899</v>
       </c>
       <c r="C8">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D8">
-        <v>0.3592655533632103</v>
+        <v>0.35926555336321031</v>
       </c>
       <c r="E8">
-        <v>0.358870467780934</v>
+        <v>0.35887046778093401</v>
       </c>
       <c r="F8">
         <v>0.353462847725036</v>
       </c>
       <c r="G8">
-        <v>0.3417773051487837</v>
+        <v>0.34177730514878368</v>
       </c>
       <c r="H8">
-        <v>0.3354348160970338</v>
+        <v>0.33543481609703379</v>
       </c>
       <c r="I8">
-        <v>0.3194734987077694</v>
+        <v>0.31947349870776942</v>
       </c>
       <c r="J8">
-        <v>0.3146991545826012</v>
+        <v>0.31469915458260123</v>
       </c>
       <c r="K8">
-        <v>0.3064144276641375</v>
+        <v>0.30641442766413751</v>
       </c>
       <c r="L8">
-        <v>0.3066462416361581</v>
+        <v>0.30664624163615811</v>
       </c>
       <c r="M8">
-        <v>0.3096497366428868</v>
+        <v>0.30964973664288681</v>
       </c>
       <c r="N8">
-        <v>0.3158136773542574</v>
+        <v>0.31581367735425742</v>
       </c>
       <c r="O8">
-        <v>0.3137546545972555</v>
+        <v>0.31375465459725549</v>
       </c>
       <c r="P8">
-        <v>0.3113495620274124</v>
+        <v>0.31134956202741237</v>
       </c>
       <c r="Q8">
-        <v>0.3100168783642657</v>
+        <v>0.31001687836426572</v>
       </c>
       <c r="R8">
-        <v>0.310166552791761</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.31016655279176097</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
       </c>
       <c r="B9">
-        <v>0.3052168244680711</v>
+        <v>0.30521682446807108</v>
       </c>
       <c r="C9">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D9">
-        <v>0.3594845625513213</v>
+        <v>0.35948456255132127</v>
       </c>
       <c r="E9">
-        <v>0.3587543453248306</v>
+        <v>0.35875434532483058</v>
       </c>
       <c r="F9">
-        <v>0.3532761753493771</v>
+        <v>0.35327617534937711</v>
       </c>
       <c r="G9">
         <v>0.3417667126897817</v>
       </c>
       <c r="H9">
-        <v>0.3352363698788079</v>
+        <v>0.33523636987880789</v>
       </c>
       <c r="I9">
-        <v>0.3180469813330111</v>
+        <v>0.31804698133301113</v>
       </c>
       <c r="J9">
         <v>0.3126020353494911</v>
       </c>
       <c r="K9">
-        <v>0.3021002593417929</v>
+        <v>0.30210025934179291</v>
       </c>
       <c r="L9">
-        <v>0.3005776265039976</v>
+        <v>0.30057762650399761</v>
       </c>
       <c r="M9">
-        <v>0.2946784426939285</v>
+        <v>0.29467844269392851</v>
       </c>
       <c r="N9">
-        <v>0.2967791951295998</v>
+        <v>0.29677919512959983</v>
       </c>
       <c r="O9">
-        <v>0.2898228617819376</v>
+        <v>0.28982286178193761</v>
       </c>
       <c r="P9">
-        <v>0.2866319897068652</v>
+        <v>0.28663198970686521</v>
       </c>
       <c r="Q9">
-        <v>0.2789253768157199</v>
+        <v>0.27892537681571988</v>
       </c>
       <c r="R9">
-        <v>0.2731259629537295</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.27312596295372948</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
       </c>
       <c r="B10">
-        <v>0.3036703504977042</v>
+        <v>0.30367035049770419</v>
       </c>
       <c r="C10">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D10">
-        <v>0.3594872179426271</v>
+        <v>0.35948721794262711</v>
       </c>
       <c r="E10">
-        <v>0.3590394652607914</v>
+        <v>0.35903946526079139</v>
       </c>
       <c r="F10">
         <v>0.3535074818555563</v>
       </c>
       <c r="G10">
-        <v>0.3421364556036404</v>
+        <v>0.34213645560364042</v>
       </c>
       <c r="H10">
-        <v>0.3347004217930771</v>
+        <v>0.33470042179307707</v>
       </c>
       <c r="I10">
-        <v>0.3180815961096244</v>
+        <v>0.31808159610962439</v>
       </c>
       <c r="J10">
-        <v>0.3125193584322314</v>
+        <v>0.31251935843223139</v>
       </c>
       <c r="K10">
-        <v>0.3019746997429777</v>
+        <v>0.30197469974297769</v>
       </c>
       <c r="L10">
-        <v>0.3002906535542877</v>
+        <v>0.30029065355428769</v>
       </c>
       <c r="M10">
-        <v>0.2938582242184936</v>
+        <v>0.29385822421849361</v>
       </c>
       <c r="N10">
-        <v>0.2958180124057821</v>
+        <v>0.29581801240578209</v>
       </c>
       <c r="O10">
-        <v>0.2894686558709698</v>
+        <v>0.28946865587096982</v>
       </c>
       <c r="P10">
-        <v>0.285056411534002</v>
+        <v>0.28505641153400202</v>
       </c>
       <c r="Q10">
-        <v>0.2767885823308759</v>
+        <v>0.27678858233087589</v>
       </c>
       <c r="R10">
-        <v>0.2711747816714434</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.27117478167144338</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>27</v>
       </c>
       <c r="B11">
-        <v>0.3060990775095974</v>
+        <v>0.30609907750959742</v>
       </c>
       <c r="C11">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D11">
         <v>0.3599246902465229</v>
       </c>
       <c r="E11">
-        <v>0.3598196542144332</v>
+        <v>0.35981965421443318</v>
       </c>
       <c r="F11">
-        <v>0.3537590995562505</v>
+        <v>0.35375909955625051</v>
       </c>
       <c r="G11">
-        <v>0.3427491994454417</v>
+        <v>0.34274919944544169</v>
       </c>
       <c r="H11">
         <v>0.3349220866891775</v>
       </c>
       <c r="I11">
-        <v>0.3178374329897832</v>
+        <v>0.31783743298978318</v>
       </c>
       <c r="J11">
         <v>0.3123308573196244</v>
       </c>
       <c r="K11">
-        <v>0.3026185561051915</v>
+        <v>0.30261855610519151</v>
       </c>
       <c r="L11">
-        <v>0.3004639107938876</v>
+        <v>0.30046391079388762</v>
       </c>
       <c r="M11">
-        <v>0.2953653961585755</v>
+        <v>0.29536539615857549</v>
       </c>
       <c r="N11">
-        <v>0.2955929331453584</v>
+        <v>0.29559293314535839</v>
       </c>
       <c r="O11">
-        <v>0.2902224168843253</v>
+        <v>0.29022241688432532</v>
       </c>
       <c r="P11">
-        <v>0.2845204298401761</v>
+        <v>0.28452042984017611</v>
       </c>
       <c r="Q11">
-        <v>0.2799296934738774</v>
+        <v>0.27992969347387742</v>
       </c>
       <c r="R11">
-        <v>0.275958375640999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.27595837564099901</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>28</v>
       </c>
       <c r="B12">
-        <v>0.3190331034222347</v>
+        <v>0.31903310342223468</v>
       </c>
       <c r="C12">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D12">
-        <v>0.357370411650472</v>
+        <v>0.35737041165047201</v>
       </c>
       <c r="E12">
-        <v>0.3569050981233802</v>
+        <v>0.35690509812338023</v>
       </c>
       <c r="F12">
         <v>0.3554630597741662</v>
       </c>
       <c r="G12">
-        <v>0.3513034822248748</v>
+        <v>0.35130348222487479</v>
       </c>
       <c r="H12">
-        <v>0.3407147461274048</v>
+        <v>0.34071474612740482</v>
       </c>
       <c r="I12">
-        <v>0.3245592656258947</v>
+        <v>0.32455926562589471</v>
       </c>
       <c r="J12">
-        <v>0.3100116318348944</v>
+        <v>0.31001163183489439</v>
       </c>
       <c r="K12">
-        <v>0.3133754209690132</v>
+        <v>0.31337542096901322</v>
       </c>
       <c r="L12">
-        <v>0.302822325260948</v>
+        <v>0.30282232526094799</v>
       </c>
       <c r="M12">
-        <v>0.2965002766801719</v>
+        <v>0.29650027668017193</v>
       </c>
       <c r="N12">
-        <v>0.2945987127547411</v>
+        <v>0.29459871275474109</v>
       </c>
       <c r="O12">
         <v>0.2939678423268407</v>
       </c>
       <c r="P12">
-        <v>0.2933107372502625</v>
+        <v>0.29331073725026252</v>
       </c>
       <c r="Q12">
-        <v>0.2941386329173212</v>
+        <v>0.29413863291732117</v>
       </c>
       <c r="R12">
-        <v>0.2982227978381893</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+        <v>0.29822279783818928</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
       </c>
       <c r="B13">
-        <v>0.3606523218512644</v>
+        <v>0.36065232185126439</v>
       </c>
       <c r="C13">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D13">
-        <v>0.3572741563596145</v>
+        <v>0.35727415635961451</v>
       </c>
       <c r="E13">
-        <v>0.3605184678124563</v>
+        <v>0.36051846781245628</v>
       </c>
       <c r="F13">
-        <v>0.3651075090886391</v>
+        <v>0.36510750908863909</v>
       </c>
       <c r="G13">
-        <v>0.364700873574431</v>
+        <v>0.36470087357443098</v>
       </c>
       <c r="H13">
-        <v>0.3475431091260585</v>
+        <v>0.34754310912605851</v>
       </c>
       <c r="I13">
-        <v>0.3487375225157235</v>
+        <v>0.34873752251572349</v>
       </c>
       <c r="J13">
-        <v>0.3397502593583427</v>
+        <v>0.33975025935834269</v>
       </c>
       <c r="K13">
-        <v>0.334247928809957</v>
+        <v>0.33424792880995702</v>
       </c>
       <c r="L13">
-        <v>0.3311867660972826</v>
+        <v>0.33118676609728259</v>
       </c>
       <c r="M13">
-        <v>0.3311027757735521</v>
+        <v>0.33110277577355213</v>
       </c>
       <c r="N13">
-        <v>0.3298934442983152</v>
+        <v>0.32989344429831519</v>
       </c>
       <c r="O13">
-        <v>0.3303301195944106</v>
+        <v>0.33033011959441061</v>
       </c>
       <c r="P13">
-        <v>0.3241697477192994</v>
+        <v>0.32416974771929941</v>
       </c>
       <c r="Q13">
-        <v>0.3240858474399732</v>
+        <v>0.32408584743997321</v>
       </c>
       <c r="R13">
-        <v>0.3215583210824484</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.32155832108244842</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>30</v>
       </c>
       <c r="B14">
         <v>0.3154716113995325</v>
       </c>
       <c r="C14">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D14">
-        <v>0.3583387004094911</v>
+        <v>0.35833870040949112</v>
       </c>
       <c r="E14">
-        <v>0.3622560723081323</v>
+        <v>0.36225607230813228</v>
       </c>
       <c r="F14">
-        <v>0.3560351959332587</v>
+        <v>0.35603519593325872</v>
       </c>
       <c r="G14">
-        <v>0.3570800732849422</v>
+        <v>0.35708007328494218</v>
       </c>
       <c r="H14">
-        <v>0.3534348541202793</v>
+        <v>0.35343485412027931</v>
       </c>
       <c r="I14">
-        <v>0.3398152863969433</v>
+        <v>0.33981528639694331</v>
       </c>
       <c r="J14">
-        <v>0.3142973580515455</v>
+        <v>0.31429735805154552</v>
       </c>
       <c r="K14">
-        <v>0.3146267836091312</v>
+        <v>0.31462678360913121</v>
       </c>
       <c r="L14">
-        <v>0.3059210646746874</v>
+        <v>0.30592106467468738</v>
       </c>
       <c r="M14">
-        <v>0.3043008195779054</v>
+        <v>0.30430081957790539</v>
       </c>
       <c r="N14">
-        <v>0.3025581310574377</v>
+        <v>0.30255813105743767</v>
       </c>
       <c r="O14">
-        <v>0.3013162044275731</v>
+        <v>0.30131620442757312</v>
       </c>
       <c r="P14">
-        <v>0.296065110238972</v>
+        <v>0.29606511023897197</v>
       </c>
       <c r="Q14">
-        <v>0.2899755342426308</v>
+        <v>0.28997553424263078</v>
       </c>
       <c r="R14">
-        <v>0.2844210632698805</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.28442106326988048</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>31</v>
       </c>
       <c r="B15">
-        <v>0.3125177588011747</v>
+        <v>0.31251775880117472</v>
       </c>
       <c r="C15">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D15">
-        <v>0.3581532650879574</v>
+        <v>0.35815326508795742</v>
       </c>
       <c r="E15">
-        <v>0.3629705447683377</v>
+        <v>0.36297054476833768</v>
       </c>
       <c r="F15">
-        <v>0.3564189822103758</v>
+        <v>0.35641898221037582</v>
       </c>
       <c r="G15">
-        <v>0.358335699188307</v>
+        <v>0.35833569918830699</v>
       </c>
       <c r="H15">
-        <v>0.3555745064973321</v>
+        <v>0.35557450649733208</v>
       </c>
       <c r="I15">
-        <v>0.3415686428308251</v>
+        <v>0.34156864283082511</v>
       </c>
       <c r="J15">
-        <v>0.3156445094749225</v>
+        <v>0.31564450947492251</v>
       </c>
       <c r="K15">
-        <v>0.3159523378441706</v>
+        <v>0.31595233784417059</v>
       </c>
       <c r="L15">
-        <v>0.3064533420882327</v>
+        <v>0.30645334208823272</v>
       </c>
       <c r="M15">
-        <v>0.3050162772409262</v>
+        <v>0.30501627724092623</v>
       </c>
       <c r="N15">
-        <v>0.3031012550108015</v>
+        <v>0.30310125501080148</v>
       </c>
       <c r="O15">
-        <v>0.3011662976350115</v>
+        <v>0.30116629763501152</v>
       </c>
       <c r="P15">
-        <v>0.2943328765704544</v>
+        <v>0.29433287657045443</v>
       </c>
       <c r="Q15">
-        <v>0.2877693106477415</v>
+        <v>0.28776931064774153</v>
       </c>
       <c r="R15">
-        <v>0.2798496826854829</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+        <v>0.27984968268548288</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>32</v>
       </c>
       <c r="B16">
-        <v>0.3119880333805136</v>
+        <v>0.31198803338051362</v>
       </c>
       <c r="C16">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D16">
         <v>0.3580543505004215</v>
       </c>
       <c r="E16">
-        <v>0.3628130609012477</v>
+        <v>0.36281306090124771</v>
       </c>
       <c r="F16">
-        <v>0.3558621017001287</v>
+        <v>0.35586210170012872</v>
       </c>
       <c r="G16">
-        <v>0.3575001413971224</v>
+        <v>0.35750014139712238</v>
       </c>
       <c r="H16">
-        <v>0.3537280560831209</v>
+        <v>0.35372805608312091</v>
       </c>
       <c r="I16">
-        <v>0.3409972048898174</v>
+        <v>0.34099720488981738</v>
       </c>
       <c r="J16">
-        <v>0.3144171022827145</v>
+        <v>0.31441710228271452</v>
       </c>
       <c r="K16">
-        <v>0.3132866839178801</v>
+        <v>0.31328668391788012</v>
       </c>
       <c r="L16">
-        <v>0.306269489794105</v>
+        <v>0.30626948979410501</v>
       </c>
       <c r="M16">
-        <v>0.304030728943202</v>
+        <v>0.30403072894320199</v>
       </c>
       <c r="N16">
         <v>0.3025586659363419</v>
       </c>
       <c r="O16">
-        <v>0.3011402776074368</v>
+        <v>0.30114027760743678</v>
       </c>
       <c r="P16">
-        <v>0.2944461754893077</v>
+        <v>0.29444617548930768</v>
       </c>
       <c r="Q16">
-        <v>0.2882915469548187</v>
+        <v>0.28829154695481868</v>
       </c>
       <c r="R16">
         <v>0.2804239608344502</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>33</v>
       </c>
       <c r="B17">
-        <v>0.3140443947076664</v>
+        <v>0.31404439470766637</v>
       </c>
       <c r="C17">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D17">
-        <v>0.3584381254379568</v>
+        <v>0.35843812543795678</v>
       </c>
       <c r="E17">
-        <v>0.3628184513260315</v>
+        <v>0.36281845132603152</v>
       </c>
       <c r="F17">
-        <v>0.3567203482629859</v>
+        <v>0.35672034826298588</v>
       </c>
       <c r="G17">
-        <v>0.3584094342829399</v>
+        <v>0.35840943428293992</v>
       </c>
       <c r="H17">
         <v>0.3563438616380642</v>
       </c>
       <c r="I17">
-        <v>0.3425868233521502</v>
+        <v>0.34258682335215018</v>
       </c>
       <c r="J17">
         <v>0.3172286056615361</v>
       </c>
       <c r="K17">
-        <v>0.3167678427527906</v>
+        <v>0.31676784275279057</v>
       </c>
       <c r="L17">
         <v>0.3082780973621379</v>
       </c>
       <c r="M17">
-        <v>0.305295151563368</v>
+        <v>0.30529515156336801</v>
       </c>
       <c r="N17">
         <v>0.303572380972147</v>
       </c>
       <c r="O17">
-        <v>0.3029838674991475</v>
+        <v>0.30298386749914752</v>
       </c>
       <c r="P17">
         <v>0.2962275913685537</v>
       </c>
       <c r="Q17">
-        <v>0.2897062108364452</v>
+        <v>0.28970621083644521</v>
       </c>
       <c r="R17">
-        <v>0.2808837698592259</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.28088376985922592</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
       </c>
       <c r="B18">
-        <v>0.3182015525278526</v>
+        <v>0.31820155252785259</v>
       </c>
       <c r="C18">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D18">
-        <v>0.35726205049717</v>
+        <v>0.35726205049717003</v>
       </c>
       <c r="E18">
-        <v>0.3568299254788116</v>
+        <v>0.35682992547881159</v>
       </c>
       <c r="F18">
-        <v>0.3561249477811522</v>
+        <v>0.35612494778115222</v>
       </c>
       <c r="G18">
-        <v>0.3517496034396499</v>
+        <v>0.35174960343964989</v>
       </c>
       <c r="H18">
-        <v>0.3412295876624202</v>
+        <v>0.34122958766242018</v>
       </c>
       <c r="I18">
         <v>0.3137842057000641</v>
       </c>
       <c r="J18">
-        <v>0.3171040110709984</v>
+        <v>0.31710401107099839</v>
       </c>
       <c r="K18">
-        <v>0.3154366876504778</v>
+        <v>0.31543668765047778</v>
       </c>
       <c r="L18">
-        <v>0.3065675564280947</v>
+        <v>0.30656755642809469</v>
       </c>
       <c r="M18">
         <v>0.3006735097548644</v>
       </c>
       <c r="N18">
-        <v>0.2979441344274764</v>
+        <v>0.29794413442747641</v>
       </c>
       <c r="O18">
-        <v>0.2967215237149519</v>
+        <v>0.29672152371495192</v>
       </c>
       <c r="P18">
-        <v>0.2946208660858449</v>
+        <v>0.29462086608584492</v>
       </c>
       <c r="Q18">
-        <v>0.2947928975330182</v>
+        <v>0.29479289753301818</v>
       </c>
       <c r="R18">
-        <v>0.2973926762572434</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.29739267625724342</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>35</v>
       </c>
       <c r="B19">
-        <v>0.3011250287872991</v>
+        <v>0.30112502878729908</v>
       </c>
       <c r="C19">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D19">
-        <v>0.3574319768050216</v>
+        <v>0.35743197680502159</v>
       </c>
       <c r="E19">
-        <v>0.3558093112437484</v>
+        <v>0.35580931124374843</v>
       </c>
       <c r="F19">
-        <v>0.3531035320732944</v>
+        <v>0.35310353207329442</v>
       </c>
       <c r="G19">
-        <v>0.3345456685530603</v>
+        <v>0.33454566855306028</v>
       </c>
       <c r="H19">
-        <v>0.3297791414935645</v>
+        <v>0.32977914149356452</v>
       </c>
       <c r="I19">
-        <v>0.308801087050543</v>
+        <v>0.30880108705054299</v>
       </c>
       <c r="J19">
-        <v>0.3084450021907877</v>
+        <v>0.30844500219078769</v>
       </c>
       <c r="K19">
-        <v>0.3016084417444334</v>
+        <v>0.30160844174443341</v>
       </c>
       <c r="L19">
-        <v>0.287633684714608</v>
+        <v>0.28763368471460798</v>
       </c>
       <c r="M19">
-        <v>0.2821804547141228</v>
+        <v>0.28218045471412279</v>
       </c>
       <c r="N19">
-        <v>0.281274903446781</v>
+        <v>0.28127490344678102</v>
       </c>
       <c r="O19">
-        <v>0.2764728103061808</v>
+        <v>0.27647281030618082</v>
       </c>
       <c r="P19">
-        <v>0.2765252510593874</v>
+        <v>0.27652525105938741</v>
       </c>
       <c r="Q19">
-        <v>0.2824349417111983</v>
+        <v>0.28243494171119832</v>
       </c>
       <c r="R19">
-        <v>0.285587102711085</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.28558710271108501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>36</v>
       </c>
       <c r="B20">
-        <v>0.2899791030152931</v>
+        <v>0.28997910301529312</v>
       </c>
       <c r="C20">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D20">
         <v>0.3579909348859282</v>
       </c>
       <c r="E20">
-        <v>0.3563908917885975</v>
+        <v>0.35639089178859751</v>
       </c>
       <c r="F20">
-        <v>0.3521991520979784</v>
+        <v>0.35219915209797842</v>
       </c>
       <c r="G20">
         <v>0.3352010386678545</v>
@@ -1518,352 +1661,340 @@
         <v>0.3243549015894886</v>
       </c>
       <c r="I20">
-        <v>0.3036423270252346</v>
+        <v>0.30364232702523458</v>
       </c>
       <c r="J20">
-        <v>0.3036272945661753</v>
+        <v>0.30362729456617532</v>
       </c>
       <c r="K20">
         <v>0.2969876996025253</v>
       </c>
       <c r="L20">
-        <v>0.2825569069983117</v>
+        <v>0.28255690699831171</v>
       </c>
       <c r="M20">
-        <v>0.2791736305867012</v>
+        <v>0.27917363058670119</v>
       </c>
       <c r="N20">
-        <v>0.2754291718264025</v>
+        <v>0.27542917182640247</v>
       </c>
       <c r="O20">
-        <v>0.2656682898334115</v>
+        <v>0.26566828983341151</v>
       </c>
       <c r="P20">
-        <v>0.2673008452759308</v>
+        <v>0.26730084527593079</v>
       </c>
       <c r="Q20">
-        <v>0.269446385358612</v>
+        <v>0.26944638535861198</v>
       </c>
       <c r="R20">
-        <v>0.269467797635084</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.26946779763508399</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>37</v>
       </c>
       <c r="B21">
-        <v>0.3300802868792044</v>
+        <v>0.33008028687920438</v>
       </c>
       <c r="C21">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D21">
-        <v>0.3575839754883089</v>
+        <v>0.35758397548830889</v>
       </c>
       <c r="E21">
-        <v>0.3569930653483803</v>
+        <v>0.35699306534838032</v>
       </c>
       <c r="F21">
-        <v>0.3568962514680347</v>
+        <v>0.35689625146803472</v>
       </c>
       <c r="G21">
-        <v>0.3545622034048397</v>
+        <v>0.35456220340483968</v>
       </c>
       <c r="H21">
-        <v>0.3350230830630851</v>
+        <v>0.33502308306308509</v>
       </c>
       <c r="I21">
         <v>0.3299106271854465</v>
       </c>
       <c r="J21">
-        <v>0.3229316254639871</v>
+        <v>0.32293162546398713</v>
       </c>
       <c r="K21">
-        <v>0.3113493250510748</v>
+        <v>0.31134932505107482</v>
       </c>
       <c r="L21">
-        <v>0.3094734868329487</v>
+        <v>0.30947348683294867</v>
       </c>
       <c r="M21">
-        <v>0.3008780235246261</v>
+        <v>0.30087802352462611</v>
       </c>
       <c r="N21">
-        <v>0.2982803569771139</v>
+        <v>0.29828035697711391</v>
       </c>
       <c r="O21">
-        <v>0.2958778665221823</v>
+        <v>0.29587786652218229</v>
       </c>
       <c r="P21">
-        <v>0.2979196224648814</v>
+        <v>0.29791962246488141</v>
       </c>
       <c r="Q21">
-        <v>0.2999066852978916</v>
+        <v>0.29990668529789161</v>
       </c>
       <c r="R21">
-        <v>0.3022974583248669</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.30229745832486687</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>38</v>
       </c>
       <c r="B22">
-        <v>0.3582998771239277</v>
+        <v>0.35829987712392769</v>
       </c>
       <c r="C22">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D22">
-        <v>0.3580242198726676</v>
+        <v>0.35802421987266758</v>
       </c>
       <c r="E22">
         <v>0.3577283286386812</v>
       </c>
       <c r="F22">
-        <v>0.3584200441991717</v>
+        <v>0.35842004419917167</v>
       </c>
       <c r="G22">
-        <v>0.3619662255505399</v>
+        <v>0.36196622555053992</v>
       </c>
       <c r="H22">
         <v>0.3467299377739243</v>
       </c>
       <c r="I22">
-        <v>0.3482057690860546</v>
+        <v>0.34820576908605461</v>
       </c>
       <c r="J22">
-        <v>0.3544783650415282</v>
+        <v>0.35447836504152819</v>
       </c>
       <c r="K22">
-        <v>0.3551736825094584</v>
+        <v>0.35517368250945841</v>
       </c>
       <c r="L22">
-        <v>0.3639419271690636</v>
+        <v>0.36394192716906359</v>
       </c>
       <c r="M22">
-        <v>0.3660958578609095</v>
+        <v>0.36609585786090948</v>
       </c>
       <c r="N22">
-        <v>0.3653684377750201</v>
+        <v>0.36536843777502009</v>
       </c>
       <c r="O22">
-        <v>0.3585483282616044</v>
+        <v>0.35854832826160438</v>
       </c>
       <c r="P22">
-        <v>0.3608717390870305</v>
+        <v>0.36087173908703052</v>
       </c>
       <c r="Q22">
-        <v>0.3592412678372424</v>
+        <v>0.35924126783724242</v>
       </c>
       <c r="R22">
-        <v>0.357138759632197</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.35713875963219699</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>39</v>
       </c>
       <c r="B23">
         <v>0.2973358124250684</v>
       </c>
       <c r="C23">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D23">
-        <v>0.3545757226597598</v>
+        <v>0.35457572265975978</v>
       </c>
       <c r="E23">
-        <v>0.3517440664724202</v>
+        <v>0.35174406647242018</v>
       </c>
       <c r="F23">
-        <v>0.3414896504599637</v>
+        <v>0.34148965045996371</v>
       </c>
       <c r="G23">
         <v>0.3262227466128102</v>
       </c>
       <c r="H23">
-        <v>0.3053684939210873</v>
+        <v>0.30536849392108728</v>
       </c>
       <c r="I23">
-        <v>0.2910705674817965</v>
+        <v>0.29107056748179649</v>
       </c>
       <c r="J23">
-        <v>0.2816327175415024</v>
+        <v>0.28163271754150238</v>
       </c>
       <c r="K23">
-        <v>0.2788470044525956</v>
+        <v>0.27884700445259558</v>
       </c>
       <c r="L23">
-        <v>0.2771313615962799</v>
+        <v>0.27713136159627988</v>
       </c>
       <c r="M23">
-        <v>0.282059508273914</v>
+        <v>0.28205950827391402</v>
       </c>
       <c r="N23">
-        <v>0.286601429855343</v>
+        <v>0.28660142985534298</v>
       </c>
       <c r="O23">
-        <v>0.2969029765816311</v>
+        <v>0.29690297658163112</v>
       </c>
       <c r="P23">
-        <v>0.2990541375483958</v>
+        <v>0.29905413754839583</v>
       </c>
       <c r="Q23">
-        <v>0.2967977147197359</v>
+        <v>0.29679771471973587</v>
       </c>
       <c r="R23">
-        <v>0.2942722668383816</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.29427226683838159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>40</v>
       </c>
       <c r="B24">
-        <v>0.2597586932436018</v>
+        <v>0.25975869324360179</v>
       </c>
       <c r="C24">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D24">
-        <v>0.3319837484654004</v>
+        <v>0.33198374846540041</v>
       </c>
       <c r="E24">
-        <v>0.3046231200272045</v>
+        <v>0.30462312002720449</v>
       </c>
       <c r="F24">
-        <v>0.2815292544868019</v>
+        <v>0.28152925448680188</v>
       </c>
       <c r="G24">
-        <v>0.2553745555177928</v>
+        <v>0.25537455551779281</v>
       </c>
       <c r="H24">
-        <v>0.2521345821326125</v>
+        <v>0.25213458213261247</v>
       </c>
       <c r="I24">
-        <v>0.2545566247362669</v>
+        <v>0.25455662473626689</v>
       </c>
       <c r="J24">
-        <v>0.2586716631474555</v>
+        <v>0.25867166314745549</v>
       </c>
       <c r="K24">
-        <v>0.2672336787700136</v>
+        <v>0.26723367877001358</v>
       </c>
       <c r="L24">
-        <v>0.2749672893293152</v>
+        <v>0.27496728932931519</v>
       </c>
       <c r="M24">
-        <v>0.2798261317593304</v>
+        <v>0.27982613175933041</v>
       </c>
       <c r="N24">
-        <v>0.2796899875570171</v>
+        <v>0.27968998755701707</v>
       </c>
       <c r="O24">
-        <v>0.2861735223102211</v>
+        <v>0.28617352231022108</v>
       </c>
       <c r="P24">
-        <v>0.2946584498888862</v>
+        <v>0.29465844988888618</v>
       </c>
       <c r="Q24">
-        <v>0.2952371177475722</v>
+        <v>0.29523711774757222</v>
       </c>
       <c r="R24">
-        <v>0.2968434187014783</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.29684341870147829</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>41</v>
       </c>
       <c r="B25">
-        <v>0.2695116856557617</v>
+        <v>0.26951168565576172</v>
       </c>
       <c r="C25">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D25">
-        <v>0.3077317948792265</v>
+        <v>0.30773179487922647</v>
       </c>
       <c r="E25">
-        <v>0.2693687547436145</v>
+        <v>0.26936875474361449</v>
       </c>
       <c r="F25">
         <v>0.2665215804546085</v>
       </c>
       <c r="G25">
-        <v>0.2648901954628096</v>
+        <v>0.26489019546280962</v>
       </c>
       <c r="H25">
-        <v>0.2665556479902206</v>
+        <v>0.26655564799022058</v>
       </c>
       <c r="I25">
-        <v>0.2686488629397666</v>
+        <v>0.26864886293976659</v>
       </c>
       <c r="J25">
-        <v>0.2803347122083344</v>
+        <v>0.28033471220833439</v>
       </c>
       <c r="K25">
-        <v>0.2791449249510389</v>
+        <v>0.27914492495103888</v>
       </c>
       <c r="L25">
         <v>0.2819500496826654</v>
       </c>
       <c r="M25">
-        <v>0.28676171415671</v>
+        <v>0.28676171415670998</v>
       </c>
       <c r="N25">
-        <v>0.2915903166835945</v>
+        <v>0.29159031668359447</v>
       </c>
       <c r="O25">
-        <v>0.3032082816599507</v>
+        <v>0.30320828165995067</v>
       </c>
       <c r="P25">
-        <v>0.3122873634712701</v>
+        <v>0.31228736347127012</v>
       </c>
       <c r="Q25">
-        <v>0.3182775181704837</v>
+        <v>0.31827751817048372</v>
       </c>
       <c r="R25">
-        <v>0.3235956794873625</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.32359567948736251</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>42</v>
       </c>
       <c r="B26">
-        <v>0.2608752171779196</v>
+        <v>0.26087521717791962</v>
       </c>
       <c r="C26">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D26">
         <v>0.3318364079848779</v>
       </c>
       <c r="E26">
-        <v>0.2881457482418786</v>
+        <v>0.28814574824187861</v>
       </c>
       <c r="F26">
-        <v>0.2655425872285674</v>
+        <v>0.26554258722856738</v>
       </c>
       <c r="G26">
-        <v>0.2523793212696714</v>
+        <v>0.25237932126967139</v>
       </c>
       <c r="H26">
-        <v>0.2419736875357621</v>
+        <v>0.24197368753576209</v>
       </c>
       <c r="I26">
         <v>0.2403408163542245</v>
@@ -1872,215 +2003,207 @@
         <v>0.2425817994819669</v>
       </c>
       <c r="K26">
-        <v>0.2426385028409415</v>
+        <v>0.24263850284094149</v>
       </c>
       <c r="L26">
         <v>0.242398419664105</v>
       </c>
       <c r="M26">
-        <v>0.239257438664131</v>
+        <v>0.23925743866413099</v>
       </c>
       <c r="N26">
         <v>0.2435938629950245</v>
       </c>
       <c r="O26">
-        <v>0.2507205220728767</v>
+        <v>0.25072052207287671</v>
       </c>
       <c r="P26">
         <v>0.2565982716006539</v>
       </c>
       <c r="Q26">
-        <v>0.2634289511010728</v>
+        <v>0.26342895110107278</v>
       </c>
       <c r="R26">
-        <v>0.2660830727441033</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.26608307274410331</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>43</v>
       </c>
       <c r="B27">
-        <v>0.2617864641665555</v>
+        <v>0.26178646416655549</v>
       </c>
       <c r="C27">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D27">
-        <v>0.3148297008343571</v>
+        <v>0.31482970083435707</v>
       </c>
       <c r="E27">
-        <v>0.2596944916217122</v>
+        <v>0.25969449162171221</v>
       </c>
       <c r="F27">
-        <v>0.2523789228460656</v>
+        <v>0.25237892284606561</v>
       </c>
       <c r="G27">
-        <v>0.2448817437538517</v>
+        <v>0.24488174375385169</v>
       </c>
       <c r="H27">
-        <v>0.2417050769724071</v>
+        <v>0.24170507697240709</v>
       </c>
       <c r="I27">
         <v>0.2385597566109971</v>
       </c>
       <c r="J27">
-        <v>0.2367221144189607</v>
+        <v>0.23672211441896071</v>
       </c>
       <c r="K27">
-        <v>0.2395946155283556</v>
+        <v>0.23959461552835559</v>
       </c>
       <c r="L27">
-        <v>0.2436437061738981</v>
+        <v>0.24364370617389811</v>
       </c>
       <c r="M27">
-        <v>0.2430614726739115</v>
+        <v>0.24306147267391151</v>
       </c>
       <c r="N27">
-        <v>0.2495021629524511</v>
+        <v>0.24950216295245109</v>
       </c>
       <c r="O27">
         <v>0.2566280798512508</v>
       </c>
       <c r="P27">
-        <v>0.2629528369459461</v>
+        <v>0.26295283694594612</v>
       </c>
       <c r="Q27">
         <v>0.2683706025741599</v>
       </c>
       <c r="R27">
-        <v>0.2722168252081111</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.27221682520811108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>44</v>
       </c>
       <c r="B28">
-        <v>0.3576622722616479</v>
+        <v>0.35766227226164787</v>
       </c>
       <c r="C28">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D28">
-        <v>0.3565029160949855</v>
+        <v>0.35650291609498552</v>
       </c>
       <c r="E28">
-        <v>0.3555778147199694</v>
+        <v>0.35557781471996941</v>
       </c>
       <c r="F28">
-        <v>0.3430310265610984</v>
+        <v>0.34303102656109841</v>
       </c>
       <c r="G28">
-        <v>0.3389975764265858</v>
+        <v>0.33899757642658579</v>
       </c>
       <c r="H28">
-        <v>0.3324997711390614</v>
+        <v>0.33249977113906137</v>
       </c>
       <c r="I28">
         <v>0.3296939738894859</v>
       </c>
       <c r="J28">
-        <v>0.3269478928679804</v>
+        <v>0.32694789286798043</v>
       </c>
       <c r="K28">
-        <v>0.3267807731033263</v>
+        <v>0.32678077310332632</v>
       </c>
       <c r="L28">
-        <v>0.3332600250205137</v>
+        <v>0.33326002502051372</v>
       </c>
       <c r="M28">
-        <v>0.3433549316827808</v>
+        <v>0.34335493168278081</v>
       </c>
       <c r="N28">
-        <v>0.3595129295744278</v>
+        <v>0.35951292957442782</v>
       </c>
       <c r="O28">
-        <v>0.3720912992327565</v>
+        <v>0.37209129923275652</v>
       </c>
       <c r="P28">
-        <v>0.3701419589572484</v>
+        <v>0.37014195895724838</v>
       </c>
       <c r="Q28">
-        <v>0.3741520741120904</v>
+        <v>0.37415207411209039</v>
       </c>
       <c r="R28">
-        <v>0.3854164724442478</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.38541647244424782</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>45</v>
       </c>
       <c r="B29">
-        <v>0.3415141968106086</v>
+        <v>0.34151419681060857</v>
       </c>
       <c r="C29">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D29">
-        <v>0.3568052905338566</v>
+        <v>0.35680529053385662</v>
       </c>
       <c r="E29">
-        <v>0.3555752416019647</v>
+        <v>0.35557524160196469</v>
       </c>
       <c r="F29">
         <v>0.3441630472468441</v>
       </c>
       <c r="G29">
-        <v>0.3391923357644107</v>
+        <v>0.33919233576441071</v>
       </c>
       <c r="H29">
-        <v>0.3290639571060934</v>
+        <v>0.32906395710609337</v>
       </c>
       <c r="I29">
-        <v>0.3240300954604802</v>
+        <v>0.32403009546048023</v>
       </c>
       <c r="J29">
-        <v>0.3097479448742851</v>
+        <v>0.30974794487428509</v>
       </c>
       <c r="K29">
-        <v>0.3165153773596678</v>
+        <v>0.31651537735966778</v>
       </c>
       <c r="L29">
-        <v>0.3147477241467725</v>
+        <v>0.31474772414677249</v>
       </c>
       <c r="M29">
-        <v>0.3181927750600476</v>
+        <v>0.31819277506004762</v>
       </c>
       <c r="N29">
-        <v>0.3214144174406898</v>
+        <v>0.32141441744068983</v>
       </c>
       <c r="O29">
-        <v>0.3302771049939781</v>
+        <v>0.33027710499397811</v>
       </c>
       <c r="P29">
-        <v>0.3350647638199858</v>
+        <v>0.33506476381998579</v>
       </c>
       <c r="Q29">
-        <v>0.3366588355371111</v>
+        <v>0.33665883553711112</v>
       </c>
       <c r="R29">
-        <v>0.3371945580800521</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.33719455808005211</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>46</v>
       </c>
       <c r="B30">
-        <v>0.3590196489606913</v>
+        <v>0.35901964896069127</v>
       </c>
       <c r="C30">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D30">
         <v>0.3560243275879883</v>
@@ -2089,68 +2212,66 @@
         <v>0.3506312907725686</v>
       </c>
       <c r="F30">
-        <v>0.3408265771016111</v>
+        <v>0.34082657710161107</v>
       </c>
       <c r="G30">
-        <v>0.3387609733363529</v>
+        <v>0.33876097333635291</v>
       </c>
       <c r="H30">
-        <v>0.3338317374478907</v>
+        <v>0.33383173744789069</v>
       </c>
       <c r="I30">
-        <v>0.3298843553621482</v>
+        <v>0.32988435536214822</v>
       </c>
       <c r="J30">
-        <v>0.3288571307064108</v>
+        <v>0.32885713070641082</v>
       </c>
       <c r="K30">
-        <v>0.3342371399419373</v>
+        <v>0.33423713994193732</v>
       </c>
       <c r="L30">
-        <v>0.3454335591987535</v>
+        <v>0.34543355919875351</v>
       </c>
       <c r="M30">
-        <v>0.3467293593197113</v>
+        <v>0.34672935931971133</v>
       </c>
       <c r="N30">
-        <v>0.3474753644449208</v>
+        <v>0.34747536444492078</v>
       </c>
       <c r="O30">
-        <v>0.3586036205037268</v>
+        <v>0.35860362050372679</v>
       </c>
       <c r="P30">
-        <v>0.3674224505427569</v>
+        <v>0.36742245054275691</v>
       </c>
       <c r="Q30">
-        <v>0.3678418713258019</v>
+        <v>0.36784187132580187</v>
       </c>
       <c r="R30">
-        <v>0.377310914749496</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.37731091474949602</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>47</v>
       </c>
       <c r="B31">
-        <v>0.3509348554451411</v>
+        <v>0.35093485544514108</v>
       </c>
       <c r="C31">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D31">
-        <v>0.3559805805511571</v>
+        <v>0.35598058055115711</v>
       </c>
       <c r="E31">
-        <v>0.3509016094610599</v>
+        <v>0.35090160946105992</v>
       </c>
       <c r="F31">
-        <v>0.3405144835759455</v>
+        <v>0.34051448357594549</v>
       </c>
       <c r="G31">
-        <v>0.3381388441765144</v>
+        <v>0.33813884417651441</v>
       </c>
       <c r="H31">
         <v>0.3334310581440007</v>
@@ -2159,56 +2280,54 @@
         <v>0.328634140606408</v>
       </c>
       <c r="J31">
-        <v>0.3263439663066955</v>
+        <v>0.32634396630669549</v>
       </c>
       <c r="K31">
-        <v>0.3270226524012418</v>
+        <v>0.32702265240124179</v>
       </c>
       <c r="L31">
-        <v>0.3281512971078108</v>
+        <v>0.32815129710781082</v>
       </c>
       <c r="M31">
         <v>0.3257802294550371</v>
       </c>
       <c r="N31">
-        <v>0.3232600277596969</v>
+        <v>0.32326002775969692</v>
       </c>
       <c r="O31">
-        <v>0.3265614143752459</v>
+        <v>0.32656141437524588</v>
       </c>
       <c r="P31">
-        <v>0.3305756316700293</v>
+        <v>0.33057563167002929</v>
       </c>
       <c r="Q31">
-        <v>0.3274409535594363</v>
+        <v>0.32744095355943631</v>
       </c>
       <c r="R31">
-        <v>0.3203553142850408</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.32035531428504083</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>48</v>
       </c>
       <c r="B32">
-        <v>0.3337401428296248</v>
+        <v>0.33374014282962478</v>
       </c>
       <c r="C32">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D32">
-        <v>0.356473670254264</v>
+        <v>0.35647367025426402</v>
       </c>
       <c r="E32">
-        <v>0.3547582275952625</v>
+        <v>0.35475822759526249</v>
       </c>
       <c r="F32">
-        <v>0.3433794704199646</v>
+        <v>0.34337947041996458</v>
       </c>
       <c r="G32">
-        <v>0.3379727573604557</v>
+        <v>0.33797275736045568</v>
       </c>
       <c r="H32">
         <v>0.3272335805147038</v>
@@ -2217,575 +2336,555 @@
         <v>0.3222737207353184</v>
       </c>
       <c r="J32">
-        <v>0.3087270997951536</v>
+        <v>0.30872709979515361</v>
       </c>
       <c r="K32">
-        <v>0.31341322238261</v>
+        <v>0.31341322238260999</v>
       </c>
       <c r="L32">
-        <v>0.3112300159501392</v>
+        <v>0.31123001595013922</v>
       </c>
       <c r="M32">
-        <v>0.3109475129369708</v>
+        <v>0.31094751293697082</v>
       </c>
       <c r="N32">
-        <v>0.3112920081249191</v>
+        <v>0.31129200812491908</v>
       </c>
       <c r="O32">
         <v>0.3115958214837225</v>
       </c>
       <c r="P32">
-        <v>0.3119242514057117</v>
+        <v>0.31192425140571173</v>
       </c>
       <c r="Q32">
-        <v>0.3220038307221907</v>
+        <v>0.32200383072219069</v>
       </c>
       <c r="R32">
-        <v>0.3193531136059755</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.31935311360597551</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>49</v>
       </c>
       <c r="B33">
-        <v>0.3331325196923413</v>
+        <v>0.33313251969234131</v>
       </c>
       <c r="C33">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D33">
-        <v>0.3562536060721889</v>
+        <v>0.35625360607218892</v>
       </c>
       <c r="E33">
-        <v>0.3542528304787138</v>
+        <v>0.35425283047871381</v>
       </c>
       <c r="F33">
-        <v>0.3432474045861674</v>
+        <v>0.34324740458616743</v>
       </c>
       <c r="G33">
-        <v>0.3377645695127576</v>
+        <v>0.33776456951275757</v>
       </c>
       <c r="H33">
-        <v>0.3274066697125588</v>
+        <v>0.32740666971255877</v>
       </c>
       <c r="I33">
-        <v>0.3229350961626548</v>
+        <v>0.32293509616265481</v>
       </c>
       <c r="J33">
-        <v>0.3086847629324793</v>
+        <v>0.30868476293247932</v>
       </c>
       <c r="K33">
-        <v>0.313660819715062</v>
+        <v>0.31366081971506199</v>
       </c>
       <c r="L33">
-        <v>0.310750278283291</v>
+        <v>0.31075027828329099</v>
       </c>
       <c r="M33">
-        <v>0.3109971999356499</v>
+        <v>0.31099719993564989</v>
       </c>
       <c r="N33">
-        <v>0.3104996025252397</v>
+        <v>0.31049960252523973</v>
       </c>
       <c r="O33">
-        <v>0.3096200660705533</v>
+        <v>0.30962006607055331</v>
       </c>
       <c r="P33">
-        <v>0.3083436047298191</v>
+        <v>0.30834360472981909</v>
       </c>
       <c r="Q33">
-        <v>0.3170642458650472</v>
+        <v>0.31706424586504722</v>
       </c>
       <c r="R33">
-        <v>0.3132451439236729</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>0.31324514392367292</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>50</v>
       </c>
       <c r="B34">
-        <v>0.3332339992188998</v>
+        <v>0.33323399921889979</v>
       </c>
       <c r="C34">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D34">
-        <v>0.3564799132916669</v>
+        <v>0.35647991329166689</v>
       </c>
       <c r="E34">
-        <v>0.3542448297266138</v>
+        <v>0.35424482972661381</v>
       </c>
       <c r="F34">
-        <v>0.343196828207346</v>
+        <v>0.34319682820734598</v>
       </c>
       <c r="G34">
-        <v>0.3380744360717082</v>
+        <v>0.33807443607170817</v>
       </c>
       <c r="H34">
-        <v>0.3277269900806249</v>
+        <v>0.32772699008062489</v>
       </c>
       <c r="I34">
-        <v>0.3226285854158892</v>
+        <v>0.32262858541588918</v>
       </c>
       <c r="J34">
         <v>0.3093332825024</v>
       </c>
       <c r="K34">
-        <v>0.3144192060577986</v>
+        <v>0.31441920605779861</v>
       </c>
       <c r="L34">
-        <v>0.311381180431732</v>
+        <v>0.31138118043173202</v>
       </c>
       <c r="M34">
-        <v>0.3114038092698359</v>
+        <v>0.31140380926983591</v>
       </c>
       <c r="N34">
-        <v>0.3113821050056803</v>
+        <v>0.31138210500568031</v>
       </c>
       <c r="O34">
-        <v>0.3101612574622833</v>
+        <v>0.31016125746228329</v>
       </c>
       <c r="P34">
-        <v>0.3084818577385536</v>
+        <v>0.30848185773855358</v>
       </c>
       <c r="Q34">
-        <v>0.3170796879068482</v>
+        <v>0.31707968790684821</v>
       </c>
       <c r="R34">
-        <v>0.3124540016747807</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+        <v>0.31245400167478071</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>51</v>
       </c>
       <c r="B35">
-        <v>0.3315996000816517</v>
+        <v>0.33159960008165168</v>
       </c>
       <c r="C35">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D35">
-        <v>0.3565430204109261</v>
+        <v>0.35654302041092611</v>
       </c>
       <c r="E35">
-        <v>0.3549671901250033</v>
+        <v>0.35496719012500327</v>
       </c>
       <c r="F35">
-        <v>0.3435621029931133</v>
+        <v>0.34356210299311329</v>
       </c>
       <c r="G35">
-        <v>0.3387525521592522</v>
+        <v>0.33875255215925221</v>
       </c>
       <c r="H35">
-        <v>0.3290026400110015</v>
+        <v>0.32900264001100149</v>
       </c>
       <c r="I35">
-        <v>0.3238703058343541</v>
+        <v>0.32387030583435411</v>
       </c>
       <c r="J35">
-        <v>0.3096663995412227</v>
+        <v>0.30966639954122271</v>
       </c>
       <c r="K35">
-        <v>0.3137572111648346</v>
+        <v>0.31375721116483463</v>
       </c>
       <c r="L35">
-        <v>0.3103597546857549</v>
+        <v>0.31035975468575489</v>
       </c>
       <c r="M35">
-        <v>0.3100435942886763</v>
+        <v>0.31004359428867628</v>
       </c>
       <c r="N35">
-        <v>0.3096249402940535</v>
+        <v>0.30962494029405352</v>
       </c>
       <c r="O35">
         <v>0.3078041473274899</v>
       </c>
       <c r="P35">
-        <v>0.3048516011069217</v>
+        <v>0.30485160110692172</v>
       </c>
       <c r="Q35">
-        <v>0.3116430209184978</v>
+        <v>0.31164302091849783</v>
       </c>
       <c r="R35">
-        <v>0.3055714206700206</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.30557142067002058</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>52</v>
       </c>
       <c r="B36">
-        <v>0.3370275979719041</v>
+        <v>0.33702759797190412</v>
       </c>
       <c r="C36">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D36">
-        <v>0.356172508610232</v>
+        <v>0.35617250861023197</v>
       </c>
       <c r="E36">
-        <v>0.3543435554701602</v>
+        <v>0.35434355547016022</v>
       </c>
       <c r="F36">
-        <v>0.342687968986033</v>
+        <v>0.34268796898603299</v>
       </c>
       <c r="G36">
-        <v>0.3383073694661465</v>
+        <v>0.33830736946614648</v>
       </c>
       <c r="H36">
-        <v>0.3279596557614449</v>
+        <v>0.32795965576144492</v>
       </c>
       <c r="I36">
-        <v>0.3231491267594047</v>
+        <v>0.32314912675940471</v>
       </c>
       <c r="J36">
-        <v>0.309223997418099</v>
+        <v>0.30922399741809897</v>
       </c>
       <c r="K36">
-        <v>0.3129431739912163</v>
+        <v>0.31294317399121629</v>
       </c>
       <c r="L36">
-        <v>0.3097459913533656</v>
+        <v>0.30974599135336561</v>
       </c>
       <c r="M36">
-        <v>0.3101703804044202</v>
+        <v>0.31017038040442019</v>
       </c>
       <c r="N36">
-        <v>0.3112077928111088</v>
+        <v>0.31120779281110877</v>
       </c>
       <c r="O36">
-        <v>0.3151472828026519</v>
+        <v>0.31514728280265192</v>
       </c>
       <c r="P36">
-        <v>0.3192980393922116</v>
+        <v>0.31929803939221157</v>
       </c>
       <c r="Q36">
-        <v>0.3275573101766865</v>
+        <v>0.32755731017668649</v>
       </c>
       <c r="R36">
-        <v>0.3255456652047204</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>0.32554566520472039</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>53</v>
       </c>
       <c r="B37">
-        <v>0.3355765916991857</v>
+        <v>0.33557659169918569</v>
       </c>
       <c r="C37">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D37">
-        <v>0.3563279194677894</v>
+        <v>0.35632791946778941</v>
       </c>
       <c r="E37">
-        <v>0.354392028358581</v>
+        <v>0.35439202835858102</v>
       </c>
       <c r="F37">
-        <v>0.3436708216448647</v>
+        <v>0.34367082164486468</v>
       </c>
       <c r="G37">
-        <v>0.3380079438712535</v>
+        <v>0.33800794387125349</v>
       </c>
       <c r="H37">
-        <v>0.3274450154375115</v>
+        <v>0.32744501543751148</v>
       </c>
       <c r="I37">
-        <v>0.3230907624664736</v>
+        <v>0.32309076246647361</v>
       </c>
       <c r="J37">
-        <v>0.3085620482087527</v>
+        <v>0.30856204820875271</v>
       </c>
       <c r="K37">
-        <v>0.3136011619083148</v>
+        <v>0.31360116190831477</v>
       </c>
       <c r="L37">
-        <v>0.3108450801407757</v>
+        <v>0.31084508014077572</v>
       </c>
       <c r="M37">
-        <v>0.3109623969115177</v>
+        <v>0.31096239691151772</v>
       </c>
       <c r="N37">
-        <v>0.3113185678148327</v>
+        <v>0.31131856781483269</v>
       </c>
       <c r="O37">
         <v>0.3140796431823612</v>
       </c>
       <c r="P37">
-        <v>0.3175624190062266</v>
+        <v>0.31756241900622662</v>
       </c>
       <c r="Q37">
-        <v>0.3254360661249068</v>
+        <v>0.32543606612490678</v>
       </c>
       <c r="R37">
-        <v>0.3225490288856294</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>0.32254902888562942</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>54</v>
       </c>
       <c r="B38">
-        <v>0.3364489560830284</v>
+        <v>0.33644895608302838</v>
       </c>
       <c r="C38">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D38">
-        <v>0.3565002873803237</v>
+        <v>0.35650028738032369</v>
       </c>
       <c r="E38">
-        <v>0.354308559936716</v>
+        <v>0.35430855993671601</v>
       </c>
       <c r="F38">
-        <v>0.3431170053511525</v>
+        <v>0.34311700535115253</v>
       </c>
       <c r="G38">
-        <v>0.337872727105457</v>
+        <v>0.33787272710545702</v>
       </c>
       <c r="H38">
         <v>0.3278328777852258</v>
       </c>
       <c r="I38">
-        <v>0.3227646618523511</v>
+        <v>0.32276466185235109</v>
       </c>
       <c r="J38">
-        <v>0.3092360169010203</v>
+        <v>0.30923601690102032</v>
       </c>
       <c r="K38">
-        <v>0.3138119726874274</v>
+        <v>0.31381197268742739</v>
       </c>
       <c r="L38">
-        <v>0.3109978214680688</v>
+        <v>0.31099782146806881</v>
       </c>
       <c r="M38">
         <v>0.3102805251359731</v>
       </c>
       <c r="N38">
-        <v>0.31051040858428</v>
+        <v>0.31051040858427997</v>
       </c>
       <c r="O38">
-        <v>0.3140878314574269</v>
+        <v>0.31408783145742691</v>
       </c>
       <c r="P38">
-        <v>0.3169765878839889</v>
+        <v>0.31697658788398891</v>
       </c>
       <c r="Q38">
-        <v>0.3232376389019492</v>
+        <v>0.32323763890194918</v>
       </c>
       <c r="R38">
-        <v>0.3212517523130959</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.32125175231309588</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>55</v>
       </c>
       <c r="B39">
-        <v>0.3344772964325005</v>
+        <v>0.33447729643250051</v>
       </c>
       <c r="C39">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D39">
-        <v>0.3557761673751799</v>
+        <v>0.35577616737517992</v>
       </c>
       <c r="E39">
-        <v>0.3537924798784859</v>
+        <v>0.35379247987848589</v>
       </c>
       <c r="F39">
-        <v>0.3423363070470676</v>
+        <v>0.34233630704706758</v>
       </c>
       <c r="G39">
         <v>0.3370200759780681</v>
       </c>
       <c r="H39">
-        <v>0.3270083867828925</v>
+        <v>0.32700838678289251</v>
       </c>
       <c r="I39">
-        <v>0.3224288300807082</v>
+        <v>0.32242883008070822</v>
       </c>
       <c r="J39">
-        <v>0.3070649221546757</v>
+        <v>0.30706492215467568</v>
       </c>
       <c r="K39">
-        <v>0.3130819948698753</v>
+        <v>0.31308199486987531</v>
       </c>
       <c r="L39">
-        <v>0.3103774644071914</v>
+        <v>0.31037746440719138</v>
       </c>
       <c r="M39">
-        <v>0.3094545826287708</v>
+        <v>0.30945458262877079</v>
       </c>
       <c r="N39">
-        <v>0.3093414670284536</v>
+        <v>0.30934146702845361</v>
       </c>
       <c r="O39">
-        <v>0.3116089042974678</v>
+        <v>0.31160890429746779</v>
       </c>
       <c r="P39">
-        <v>0.3137545893594176</v>
+        <v>0.31375458935941758</v>
       </c>
       <c r="Q39">
-        <v>0.3182181194881155</v>
+        <v>0.31821811948811551</v>
       </c>
       <c r="R39">
-        <v>0.3162558926453458</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.31625589264534582</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>56</v>
       </c>
       <c r="B40">
-        <v>0.3329559341932019</v>
+        <v>0.33295593419320191</v>
       </c>
       <c r="C40">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D40">
-        <v>0.3568378440149368</v>
+        <v>0.35683784401493679</v>
       </c>
       <c r="E40">
-        <v>0.355571985726006</v>
+        <v>0.35557198572600601</v>
       </c>
       <c r="F40">
-        <v>0.3436829629873057</v>
+        <v>0.34368296298730572</v>
       </c>
       <c r="G40">
-        <v>0.339281191874636</v>
+        <v>0.33928119187463601</v>
       </c>
       <c r="H40">
-        <v>0.3284809770128349</v>
+        <v>0.32848097701283491</v>
       </c>
       <c r="I40">
-        <v>0.3236645097742443</v>
+        <v>0.32366450977424432</v>
       </c>
       <c r="J40">
-        <v>0.309091073841368</v>
+        <v>0.30909107384136802</v>
       </c>
       <c r="K40">
-        <v>0.3136225305620042</v>
+        <v>0.31362253056200418</v>
       </c>
       <c r="L40">
-        <v>0.3099897371580744</v>
+        <v>0.30998973715807437</v>
       </c>
       <c r="M40">
-        <v>0.3095198979637304</v>
+        <v>0.30951989796373042</v>
       </c>
       <c r="N40">
-        <v>0.30814727788823</v>
+        <v>0.30814727788822999</v>
       </c>
       <c r="O40">
         <v>0.308028267628699</v>
       </c>
       <c r="P40">
-        <v>0.3067530328724635</v>
+        <v>0.30675303287246353</v>
       </c>
       <c r="Q40">
-        <v>0.3129470712227947</v>
+        <v>0.31294707122279469</v>
       </c>
       <c r="R40">
-        <v>0.3080154193502734</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.30801541935027338</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>57</v>
       </c>
       <c r="B41">
-        <v>0.3530251313660251</v>
+        <v>0.35302513136602509</v>
       </c>
       <c r="C41">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D41">
-        <v>0.3523424752955024</v>
+        <v>0.35234247529550239</v>
       </c>
       <c r="E41">
-        <v>0.3562231943314818</v>
+        <v>0.35622319433148181</v>
       </c>
       <c r="F41">
-        <v>0.3447093065822233</v>
+        <v>0.34470930658222332</v>
       </c>
       <c r="G41">
-        <v>0.3400561394397874</v>
+        <v>0.34005613943978741</v>
       </c>
       <c r="H41">
-        <v>0.3400257030989534</v>
+        <v>0.34002570309895341</v>
       </c>
       <c r="I41">
-        <v>0.346772643559232</v>
+        <v>0.34677264355923199</v>
       </c>
       <c r="J41">
-        <v>0.3654943469452883</v>
+        <v>0.36549434694528832</v>
       </c>
       <c r="K41">
         <v>0.3808217453075059</v>
       </c>
       <c r="L41">
-        <v>0.3867545119372057</v>
+        <v>0.38675451193720572</v>
       </c>
       <c r="M41">
-        <v>0.3973212767276292</v>
+        <v>0.39732127672762918</v>
       </c>
       <c r="N41">
-        <v>0.4048273138634353</v>
+        <v>0.40482731386343529</v>
       </c>
       <c r="O41">
-        <v>0.410172830378461</v>
+        <v>0.41017283037846097</v>
       </c>
       <c r="P41">
-        <v>0.4081817472716163</v>
+        <v>0.40818174727161632</v>
       </c>
       <c r="Q41">
-        <v>0.3983178249485571</v>
+        <v>0.39831782494855711</v>
       </c>
       <c r="R41">
-        <v>0.3877490602407918</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>0.38774906024079181</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>58</v>
       </c>
       <c r="B42">
-        <v>0.3535649688738627</v>
+        <v>0.35356496887386268</v>
       </c>
       <c r="C42">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D42">
-        <v>0.352283934618403</v>
+        <v>0.35228393461840302</v>
       </c>
       <c r="E42">
-        <v>0.3529072989902707</v>
+        <v>0.35290729899027068</v>
       </c>
       <c r="F42">
-        <v>0.3393933414756931</v>
+        <v>0.33939334147569311</v>
       </c>
       <c r="G42">
         <v>0.329331786177052</v>
@@ -2794,327 +2893,329 @@
         <v>0.3287707929433285</v>
       </c>
       <c r="I42">
-        <v>0.3308080439803803</v>
+        <v>0.33080804398038027</v>
       </c>
       <c r="J42">
         <v>0.3422300588109255</v>
       </c>
       <c r="K42">
-        <v>0.3524131227361175</v>
+        <v>0.35241312273611752</v>
       </c>
       <c r="L42">
-        <v>0.3565384080292536</v>
+        <v>0.35653840802925357</v>
       </c>
       <c r="M42">
-        <v>0.3635527058837533</v>
+        <v>0.36355270588375332</v>
       </c>
       <c r="N42">
-        <v>0.3626020980525643</v>
+        <v>0.36260209805256433</v>
       </c>
       <c r="O42">
-        <v>0.3443505905386539</v>
+        <v>0.34435059053865391</v>
       </c>
       <c r="P42">
-        <v>0.3342592151028224</v>
+        <v>0.33425921510282242</v>
       </c>
       <c r="Q42">
-        <v>0.3295027524827989</v>
+        <v>0.32950275248279892</v>
       </c>
       <c r="R42">
-        <v>0.320139443692913</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.32013944369291297</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>59</v>
       </c>
       <c r="B43">
-        <v>0.3482514326212759</v>
+        <v>0.34825143262127589</v>
       </c>
       <c r="C43">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D43">
-        <v>0.3522575560762596</v>
+        <v>0.35225755607625958</v>
       </c>
       <c r="E43">
-        <v>0.351925238570955</v>
+        <v>0.35192523857095498</v>
       </c>
       <c r="F43">
-        <v>0.3385472673954356</v>
+        <v>0.33854726739543561</v>
       </c>
       <c r="G43">
-        <v>0.3272608496264973</v>
+        <v>0.32726084962649732</v>
       </c>
       <c r="H43">
-        <v>0.3273208855536254</v>
+        <v>0.32732088555362537</v>
       </c>
       <c r="I43">
-        <v>0.328507546263524</v>
+        <v>0.32850754626352402</v>
       </c>
       <c r="J43">
-        <v>0.3347959891495007</v>
+        <v>0.33479598914950071</v>
       </c>
       <c r="K43">
-        <v>0.3409100795555822</v>
+        <v>0.34091007955558222</v>
       </c>
       <c r="L43">
         <v>0.3486963520009535</v>
       </c>
       <c r="M43">
-        <v>0.3443267356302516</v>
+        <v>0.34432673563025162</v>
       </c>
       <c r="N43">
-        <v>0.3427394457547728</v>
+        <v>0.34273944575477278</v>
       </c>
       <c r="O43">
-        <v>0.3244164988407163</v>
+        <v>0.32441649884071633</v>
       </c>
       <c r="P43">
-        <v>0.3252505515840999</v>
+        <v>0.32525055158409988</v>
       </c>
       <c r="Q43">
-        <v>0.3112857392555543</v>
+        <v>0.31128573925555431</v>
       </c>
       <c r="R43">
-        <v>0.298258138776678</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
+        <v>0.29825813877667801</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>60</v>
       </c>
       <c r="B44">
-        <v>0.3501535056317626</v>
+        <v>0.35015350563176262</v>
       </c>
       <c r="C44">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D44">
-        <v>0.3501535056317626</v>
+        <v>0.35015350563176262</v>
       </c>
       <c r="E44">
-        <v>0.3577379535958485</v>
+        <v>0.35773795359584848</v>
       </c>
       <c r="F44">
-        <v>0.348961781830784</v>
+        <v>0.34896178183078402</v>
       </c>
       <c r="G44">
         <v>0.345015270629772</v>
       </c>
       <c r="H44">
-        <v>0.3503334773651604</v>
+        <v>0.35033347736516041</v>
       </c>
       <c r="I44">
-        <v>0.3642287456123636</v>
+        <v>0.36422874561236362</v>
       </c>
       <c r="J44">
-        <v>0.3729681592564565</v>
+        <v>0.37296815925645649</v>
       </c>
       <c r="K44">
-        <v>0.3769912497820512</v>
+        <v>0.37699124978205117</v>
       </c>
       <c r="L44">
-        <v>0.3710657506319727</v>
+        <v>0.37106575063197272</v>
       </c>
       <c r="M44">
         <v>0.3866733399989184</v>
       </c>
       <c r="N44">
-        <v>0.3857557734941846</v>
+        <v>0.38575577349418461</v>
       </c>
       <c r="O44">
-        <v>0.381453500669076</v>
+        <v>0.38145350066907602</v>
       </c>
       <c r="P44">
-        <v>0.3816846252743543</v>
+        <v>0.38168462527435432</v>
       </c>
       <c r="Q44">
-        <v>0.3728728680870071</v>
+        <v>0.37287286808700709</v>
       </c>
       <c r="R44">
-        <v>0.3645552296723141</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
+        <v>0.36455522967231407</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>61</v>
       </c>
       <c r="B45">
-        <v>0.3546546161126914</v>
+        <v>0.35465461611269139</v>
       </c>
       <c r="C45">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D45">
-        <v>0.3551345748422866</v>
+        <v>0.35513457484228661</v>
       </c>
       <c r="E45">
-        <v>0.3513636244361129</v>
+        <v>0.35136362443611291</v>
       </c>
       <c r="F45">
-        <v>0.3451522192200538</v>
+        <v>0.34515221922005379</v>
       </c>
       <c r="G45">
-        <v>0.3373159650244756</v>
+        <v>0.33731596502447558</v>
       </c>
       <c r="H45">
-        <v>0.336990682530853</v>
+        <v>0.33699068253085301</v>
       </c>
       <c r="I45">
-        <v>0.3269878479861097</v>
+        <v>0.32698784798610969</v>
       </c>
       <c r="J45">
-        <v>0.3270793755194705</v>
+        <v>0.32707937551947053</v>
       </c>
       <c r="K45">
-        <v>0.3209290654117642</v>
+        <v>0.32092906541176419</v>
       </c>
       <c r="L45">
-        <v>0.3180608809194412</v>
+        <v>0.31806088091944118</v>
       </c>
       <c r="M45">
-        <v>0.3149077937742422</v>
+        <v>0.31490779377424222</v>
       </c>
       <c r="N45">
         <v>0.3208677490098874</v>
       </c>
       <c r="O45">
-        <v>0.3224887774816053</v>
+        <v>0.32248877748160532</v>
       </c>
       <c r="P45">
-        <v>0.3247139412233132</v>
+        <v>0.32471394122331321</v>
       </c>
       <c r="Q45">
-        <v>0.329216064468967</v>
+        <v>0.32921606446896701</v>
       </c>
       <c r="R45">
-        <v>0.3331387199233767</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.33313871992337668</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>62</v>
       </c>
       <c r="B46">
-        <v>0.2905404188066918</v>
+        <v>0.29054041880669179</v>
       </c>
       <c r="C46">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D46">
-        <v>0.3520601471810013</v>
+        <v>0.35206014718100131</v>
       </c>
       <c r="E46">
-        <v>0.3423594161093121</v>
+        <v>0.34235941610931209</v>
       </c>
       <c r="F46">
         <v>0.3193136459634251</v>
       </c>
       <c r="G46">
-        <v>0.2903005680852344</v>
+        <v>0.29030056808523441</v>
       </c>
       <c r="H46">
-        <v>0.2841523672965351</v>
+        <v>0.28415236729653509</v>
       </c>
       <c r="I46">
-        <v>0.2825176228047178</v>
+        <v>0.28251762280471782</v>
       </c>
       <c r="J46">
         <v>0.2811469137990209</v>
       </c>
       <c r="K46">
-        <v>0.285293673660461</v>
+        <v>0.28529367366046099</v>
       </c>
       <c r="L46">
-        <v>0.2882353479281777</v>
+        <v>0.28823534792817768</v>
       </c>
       <c r="M46">
-        <v>0.2950925481086475</v>
+        <v>0.29509254810864749</v>
       </c>
       <c r="N46">
-        <v>0.3083652289085326</v>
+        <v>0.30836522890853257</v>
       </c>
       <c r="O46">
-        <v>0.3237904970707505</v>
+        <v>0.32379049707075053</v>
       </c>
       <c r="P46">
-        <v>0.3300844273372286</v>
+        <v>0.33008442733722859</v>
       </c>
       <c r="Q46">
-        <v>0.3322649721653426</v>
+        <v>0.33226497216534262</v>
       </c>
       <c r="R46">
-        <v>0.3335225443551424</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
+        <v>0.33352254435514239</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>63</v>
       </c>
       <c r="B47">
-        <v>0.3072760375710198</v>
+        <v>0.30727603757101979</v>
       </c>
       <c r="C47">
-        <v>0.3583701912931958</v>
+        <v>0.35837019129319581</v>
       </c>
       <c r="D47">
-        <v>0.3492109034266944</v>
+        <v>0.34921090342669442</v>
       </c>
       <c r="E47">
-        <v>0.3358506557109854</v>
+        <v>0.33585065571098538</v>
       </c>
       <c r="F47">
-        <v>0.3155879023180272</v>
+        <v>0.31558790231802719</v>
       </c>
       <c r="G47">
-        <v>0.3143257592263488</v>
+        <v>0.31432575922634881</v>
       </c>
       <c r="H47">
-        <v>0.3020070351991679</v>
+        <v>0.30200703519916788</v>
       </c>
       <c r="I47">
-        <v>0.2928904798302338</v>
+        <v>0.29289047983023381</v>
       </c>
       <c r="J47">
-        <v>0.2836976182236505</v>
+        <v>0.28369761822365053</v>
       </c>
       <c r="K47">
-        <v>0.2820909541497131</v>
+        <v>0.28209095414971308</v>
       </c>
       <c r="L47">
-        <v>0.2837011062405255</v>
+        <v>0.28370110624052552</v>
       </c>
       <c r="M47">
         <v>0.2825928766809761</v>
       </c>
       <c r="N47">
-        <v>0.2877724959110645</v>
+        <v>0.28777249591106452</v>
       </c>
       <c r="O47">
-        <v>0.2996061392880086</v>
+        <v>0.29960613928800861</v>
       </c>
       <c r="P47">
-        <v>0.307217437395542</v>
+        <v>0.30721743739554203</v>
       </c>
       <c r="Q47">
-        <v>0.3149653995969975</v>
+        <v>0.31496539959699749</v>
       </c>
       <c r="R47">
-        <v>0.3257460167846307</v>
+        <v>0.32574601678463072</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C2:R47">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>